--- a/图片内容分析和注释.xlsx
+++ b/图片内容分析和注释.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="94">
   <si>
     <t>图片文件名</t>
   </si>
@@ -240,24 +240,24 @@
     <t>CSM 核心分析 - 按过渡期计量方法拆分 CSM</t>
   </si>
   <si>
+    <t>csm_comp_lat</t>
+  </si>
+  <si>
+    <t>CSM 核心分析 - 最新年摊销前 CSM 变动项占比</t>
+  </si>
+  <si>
+    <t>csm_comp_pre</t>
+  </si>
+  <si>
+    <t>CSM 核心分析 - 上一年摊销前 CSM 变动项占比</t>
+  </si>
+  <si>
     <t>csm_ratio_trend</t>
   </si>
   <si>
     <t>CSM 核心分析 -摊销比</t>
   </si>
   <si>
-    <t>csm_comp_lat</t>
-  </si>
-  <si>
-    <t>CSM 核心分析 - 最新年摊销前 CSM 变动项占比</t>
-  </si>
-  <si>
-    <t>csm_comp_pre</t>
-  </si>
-  <si>
-    <t>CSM 核心分析 - 上一年摊销前 CSM 变动项占比</t>
-  </si>
-  <si>
     <t>csm_equity</t>
   </si>
   <si>
@@ -288,16 +288,34 @@
     <t>运营效能分析 - 业务及管理费费用结构</t>
   </si>
   <si>
+    <t>discount_rate</t>
+  </si>
+  <si>
+    <t>运营效能分析 - 折现率假设</t>
+  </si>
+  <si>
+    <t>confidence_level</t>
+  </si>
+  <si>
+    <t>运营效能分析 - 非金融风险调整置信水平</t>
+  </si>
+  <si>
     <t>six_dim</t>
   </si>
   <si>
     <t>综合评价矩阵 - 财务结果六维表现</t>
   </si>
   <si>
-    <t>fin_detail</t>
+    <t>report_detail</t>
   </si>
   <si>
     <t>附录 - 保险服务业绩明细表</t>
+  </si>
+  <si>
+    <t>nbv_table</t>
+  </si>
+  <si>
+    <t>附录 - 新业务价值相关分析</t>
   </si>
 </sst>
 </file>
@@ -1506,7 +1524,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E72"/>
+  <dimension ref="A1:E74"/>
   <sheetFormatPr defaultColWidth="9.02654867256637" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="13.283185840708" customWidth="1"/>
@@ -1515,7 +1533,7 @@
     <col min="4" max="5" width="17.7256637168142" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28.5" spans="1:5">
+    <row r="1" ht="14.65" spans="1:5">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -1613,7 +1631,7 @@
       <c r="D8" s="4"/>
       <c r="E8" s="4"/>
     </row>
-    <row r="9" ht="13.9" spans="1:5">
+    <row r="9" ht="14.65" spans="1:5">
       <c r="B9" s="4" t="s">
         <v>24</v>
       </c>
@@ -1623,7 +1641,7 @@
       <c r="D9" s="4"/>
       <c r="E9" s="4"/>
     </row>
-    <row r="10" ht="14.6" spans="1:5">
+    <row r="10" ht="14.65" spans="1:5">
       <c r="B10" s="4" t="s">
         <v>26</v>
       </c>
@@ -1633,7 +1651,7 @@
       <c r="D10" s="4"/>
       <c r="E10" s="4"/>
     </row>
-    <row r="11" ht="13.9" spans="1:5">
+    <row r="11" ht="14.65" spans="1:5">
       <c r="B11" s="4" t="s">
         <v>28</v>
       </c>
@@ -1643,7 +1661,7 @@
       <c r="D11" s="4"/>
       <c r="E11" s="4"/>
     </row>
-    <row r="12" ht="13.9" spans="1:5">
+    <row r="12" ht="14.65" spans="1:5">
       <c r="B12" s="4" t="s">
         <v>30</v>
       </c>
@@ -1653,7 +1671,7 @@
       <c r="D12" s="4"/>
       <c r="E12" s="4"/>
     </row>
-    <row r="13" ht="13.9" spans="1:5">
+    <row r="13" ht="14.65" spans="1:5">
       <c r="B13" s="4" t="s">
         <v>32</v>
       </c>
@@ -1663,7 +1681,7 @@
       <c r="D13" s="4"/>
       <c r="E13" s="4"/>
     </row>
-    <row r="14" ht="13.9" spans="1:5">
+    <row r="14" ht="14.65" spans="1:5">
       <c r="B14" s="4" t="s">
         <v>34</v>
       </c>
@@ -1673,7 +1691,7 @@
       <c r="D14" s="4"/>
       <c r="E14" s="4"/>
     </row>
-    <row r="15" ht="13.9" spans="1:5">
+    <row r="15" ht="14.65" spans="1:5">
       <c r="B15" s="4" t="s">
         <v>36</v>
       </c>
@@ -1683,7 +1701,7 @@
       <c r="D15" s="4"/>
       <c r="E15" s="4"/>
     </row>
-    <row r="16" ht="13.9" spans="1:5">
+    <row r="16" ht="14.65" spans="1:5">
       <c r="B16" s="4" t="s">
         <v>38</v>
       </c>
@@ -1693,7 +1711,7 @@
       <c r="D16" s="4"/>
       <c r="E16" s="4"/>
     </row>
-    <row r="17" ht="13.9" spans="2:5">
+    <row r="17" ht="14.65" spans="2:5">
       <c r="B17" s="4" t="s">
         <v>40</v>
       </c>
@@ -1703,7 +1721,7 @@
       <c r="D17" s="4"/>
       <c r="E17" s="4"/>
     </row>
-    <row r="18" ht="13.9" spans="2:5">
+    <row r="18" ht="14.65" spans="2:5">
       <c r="B18" s="4" t="s">
         <v>42</v>
       </c>
@@ -1713,7 +1731,7 @@
       <c r="D18" s="4"/>
       <c r="E18" s="4"/>
     </row>
-    <row r="19" ht="13.9" spans="2:5">
+    <row r="19" ht="14.65" spans="2:5">
       <c r="B19" s="4" t="s">
         <v>44</v>
       </c>
@@ -1723,7 +1741,7 @@
       <c r="D19" s="4"/>
       <c r="E19" s="4"/>
     </row>
-    <row r="20" ht="13.9" spans="2:5">
+    <row r="20" ht="14.65" spans="2:5">
       <c r="B20" s="4" t="s">
         <v>46</v>
       </c>
@@ -1733,7 +1751,7 @@
       <c r="D20" s="4"/>
       <c r="E20" s="4"/>
     </row>
-    <row r="21" ht="13.9" spans="2:5">
+    <row r="21" ht="14.65" spans="2:5">
       <c r="B21" s="4" t="s">
         <v>48</v>
       </c>
@@ -1743,7 +1761,7 @@
       <c r="D21" s="4"/>
       <c r="E21" s="4"/>
     </row>
-    <row r="22" ht="13.9" spans="2:5">
+    <row r="22" ht="14.65" spans="2:5">
       <c r="B22" s="4" t="s">
         <v>50</v>
       </c>
@@ -1753,7 +1771,7 @@
       <c r="D22" s="4"/>
       <c r="E22" s="4"/>
     </row>
-    <row r="23" ht="13.9" spans="2:5">
+    <row r="23" ht="14.65" spans="2:5">
       <c r="B23" s="4" t="s">
         <v>52</v>
       </c>
@@ -1763,7 +1781,7 @@
       <c r="D23" s="4"/>
       <c r="E23" s="4"/>
     </row>
-    <row r="24" ht="13.9" spans="2:5">
+    <row r="24" ht="14.65" spans="2:5">
       <c r="B24" s="4" t="s">
         <v>54</v>
       </c>
@@ -1773,7 +1791,7 @@
       <c r="D24" s="4"/>
       <c r="E24" s="4"/>
     </row>
-    <row r="25" ht="13.9" spans="2:5">
+    <row r="25" ht="14.65" spans="2:5">
       <c r="B25" s="4" t="s">
         <v>56</v>
       </c>
@@ -1783,7 +1801,7 @@
       <c r="D25" s="4"/>
       <c r="E25" s="4"/>
     </row>
-    <row r="26" ht="13.9" spans="2:5">
+    <row r="26" ht="14.65" spans="2:5">
       <c r="B26" s="4" t="s">
         <v>58</v>
       </c>
@@ -1793,7 +1811,7 @@
       <c r="D26" s="4"/>
       <c r="E26" s="4"/>
     </row>
-    <row r="27" ht="13.9" spans="2:5">
+    <row r="27" ht="14.65" spans="2:5">
       <c r="B27" s="4" t="s">
         <v>60</v>
       </c>
@@ -1803,7 +1821,7 @@
       <c r="D27" s="4"/>
       <c r="E27" s="4"/>
     </row>
-    <row r="28" ht="13.9" spans="2:5">
+    <row r="28" ht="14.65" spans="2:5">
       <c r="B28" s="4" t="s">
         <v>62</v>
       </c>
@@ -1813,7 +1831,7 @@
       <c r="D28" s="4"/>
       <c r="E28" s="4"/>
     </row>
-    <row r="29" ht="13.9" spans="2:5">
+    <row r="29" ht="14.65" spans="2:5">
       <c r="B29" s="4" t="s">
         <v>64</v>
       </c>
@@ -1853,7 +1871,7 @@
       <c r="D32" s="4"/>
       <c r="E32" s="4"/>
     </row>
-    <row r="33" ht="13.9" spans="2:5">
+    <row r="33" ht="14.65" spans="2:5">
       <c r="B33" s="4" t="s">
         <v>72</v>
       </c>
@@ -1863,7 +1881,7 @@
       <c r="D33" s="4"/>
       <c r="E33" s="4"/>
     </row>
-    <row r="34" ht="13.9" spans="2:5">
+    <row r="34" ht="14.65" spans="2:5">
       <c r="B34" s="4" t="s">
         <v>74</v>
       </c>
@@ -1873,7 +1891,7 @@
       <c r="D34" s="4"/>
       <c r="E34" s="4"/>
     </row>
-    <row r="35" ht="13.9" spans="2:5">
+    <row r="35" ht="14.65" spans="2:5">
       <c r="B35" s="4" t="s">
         <v>76</v>
       </c>
@@ -1883,7 +1901,7 @@
       <c r="D35" s="4"/>
       <c r="E35" s="4"/>
     </row>
-    <row r="36" ht="13.9" spans="2:5">
+    <row r="36" ht="14.65" spans="2:5">
       <c r="B36" s="4" t="s">
         <v>78</v>
       </c>
@@ -1893,7 +1911,7 @@
       <c r="D36" s="4"/>
       <c r="E36" s="4"/>
     </row>
-    <row r="37" ht="13.9" spans="2:5">
+    <row r="37" ht="14.65" spans="2:5">
       <c r="B37" s="4" t="s">
         <v>80</v>
       </c>
@@ -1903,7 +1921,7 @@
       <c r="D37" s="4"/>
       <c r="E37" s="4"/>
     </row>
-    <row r="38" ht="13.9" spans="2:5">
+    <row r="38" ht="14.65" spans="2:5">
       <c r="B38" s="4" t="s">
         <v>82</v>
       </c>
@@ -1913,7 +1931,7 @@
       <c r="D38" s="4"/>
       <c r="E38" s="4"/>
     </row>
-    <row r="39" ht="13.9" spans="2:5">
+    <row r="39" ht="14.65" spans="2:5">
       <c r="B39" s="4" t="s">
         <v>84</v>
       </c>
@@ -1923,7 +1941,7 @@
       <c r="D39" s="4"/>
       <c r="E39" s="4"/>
     </row>
-    <row r="40" ht="13.9" spans="2:5">
+    <row r="40" ht="14.65" spans="2:5">
       <c r="B40" s="4" t="s">
         <v>86</v>
       </c>
@@ -1933,11 +1951,39 @@
       <c r="D40" s="4"/>
       <c r="E40" s="4"/>
     </row>
-    <row r="54" spans="2:2">
-      <c r="B54" s="6"/>
-    </row>
-    <row r="72" spans="2:2">
-      <c r="B72" s="6"/>
+    <row r="41" ht="14.65" spans="2:5">
+      <c r="B41" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="C41" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="D41" s="4"/>
+      <c r="E41" s="4"/>
+    </row>
+    <row r="42" ht="14.65" spans="2:5">
+      <c r="B42" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="C42" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="D42" s="4"/>
+      <c r="E42" s="4"/>
+    </row>
+    <row r="43" ht="14.65" spans="2:5">
+      <c r="B43" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="C43" s="5" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="56" spans="2:2">
+      <c r="B56" s="6"/>
+    </row>
+    <row r="74" spans="2:2">
+      <c r="B74" s="6"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
